--- a/resource/task1_test.xlsx
+++ b/resource/task1_test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21768" windowHeight="8904"/>
+    <workbookView windowWidth="23040" windowHeight="8904"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
     <t>任务类型</t>
   </si>
@@ -1190,8 +1190,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -1292,567 +1292,6 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1">
-        <v>6</v>
-      </c>
-      <c r="E8" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="1">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1">
-        <v>6</v>
-      </c>
-      <c r="E10" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="1">
-        <v>2</v>
-      </c>
-      <c r="C11" s="1">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1">
-        <v>6</v>
-      </c>
-      <c r="E11" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
-        <v>8</v>
-      </c>
-      <c r="D12" s="1">
-        <v>7</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1">
-        <v>7</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1">
-        <v>8</v>
-      </c>
-      <c r="D14" s="1">
-        <v>7</v>
-      </c>
-      <c r="E14" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1">
-        <v>8</v>
-      </c>
-      <c r="D15" s="1">
-        <v>7</v>
-      </c>
-      <c r="E15" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2</v>
-      </c>
-      <c r="C16" s="1">
-        <v>8</v>
-      </c>
-      <c r="D16" s="1">
-        <v>7</v>
-      </c>
-      <c r="E16" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1">
-        <v>8</v>
-      </c>
-      <c r="D17" s="1">
-        <v>7</v>
-      </c>
-      <c r="E17" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="1">
-        <v>2</v>
-      </c>
-      <c r="C18" s="1">
-        <v>8</v>
-      </c>
-      <c r="D18" s="1">
-        <v>7</v>
-      </c>
-      <c r="E18" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="1">
-        <v>2</v>
-      </c>
-      <c r="C19" s="1">
-        <v>8</v>
-      </c>
-      <c r="D19" s="1">
-        <v>8</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="1">
-        <v>2</v>
-      </c>
-      <c r="C20" s="1">
-        <v>8</v>
-      </c>
-      <c r="D20" s="1">
-        <v>8</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2</v>
-      </c>
-      <c r="C21" s="1">
-        <v>8</v>
-      </c>
-      <c r="D21" s="1">
-        <v>8</v>
-      </c>
-      <c r="E21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="1">
-        <v>2</v>
-      </c>
-      <c r="C22" s="1">
-        <v>8</v>
-      </c>
-      <c r="D22" s="1">
-        <v>8</v>
-      </c>
-      <c r="E22" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1">
-        <v>8</v>
-      </c>
-      <c r="D23" s="1">
-        <v>8</v>
-      </c>
-      <c r="E23" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="1">
-        <v>8</v>
-      </c>
-      <c r="D24" s="1">
-        <v>8</v>
-      </c>
-      <c r="E24" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1">
-        <v>8</v>
-      </c>
-      <c r="D25" s="1">
-        <v>8</v>
-      </c>
-      <c r="E25" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="1">
-        <v>2</v>
-      </c>
-      <c r="C26" s="1">
-        <v>8</v>
-      </c>
-      <c r="D26" s="1">
-        <v>9</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="1">
-        <v>2</v>
-      </c>
-      <c r="C27" s="1">
-        <v>8</v>
-      </c>
-      <c r="D27" s="1">
-        <v>9</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="1">
-        <v>2</v>
-      </c>
-      <c r="C28" s="1">
-        <v>8</v>
-      </c>
-      <c r="D28" s="1">
-        <v>9</v>
-      </c>
-      <c r="E28" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="1">
-        <v>2</v>
-      </c>
-      <c r="C29" s="1">
-        <v>8</v>
-      </c>
-      <c r="D29" s="1">
-        <v>9</v>
-      </c>
-      <c r="E29" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2</v>
-      </c>
-      <c r="C30" s="1">
-        <v>8</v>
-      </c>
-      <c r="D30" s="1">
-        <v>9</v>
-      </c>
-      <c r="E30" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2</v>
-      </c>
-      <c r="C31" s="1">
-        <v>8</v>
-      </c>
-      <c r="D31" s="1">
-        <v>9</v>
-      </c>
-      <c r="E31" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2</v>
-      </c>
-      <c r="C32" s="1">
-        <v>8</v>
-      </c>
-      <c r="D32" s="1">
-        <v>9</v>
-      </c>
-      <c r="E32" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2</v>
-      </c>
-      <c r="C33" s="1">
-        <v>8</v>
-      </c>
-      <c r="D33" s="1">
-        <v>10</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="1">
-        <v>2</v>
-      </c>
-      <c r="C34" s="1">
-        <v>8</v>
-      </c>
-      <c r="D34" s="1">
-        <v>10</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="1">
-        <v>2</v>
-      </c>
-      <c r="C35" s="1">
-        <v>8</v>
-      </c>
-      <c r="D35" s="1">
-        <v>10</v>
-      </c>
-      <c r="E35" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2</v>
-      </c>
-      <c r="C36" s="1">
-        <v>8</v>
-      </c>
-      <c r="D36" s="1">
-        <v>10</v>
-      </c>
-      <c r="E36" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="1">
-        <v>2</v>
-      </c>
-      <c r="C37" s="1">
-        <v>8</v>
-      </c>
-      <c r="D37" s="1">
-        <v>10</v>
-      </c>
-      <c r="E37" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="1">
-        <v>2</v>
-      </c>
-      <c r="C38" s="1">
-        <v>8</v>
-      </c>
-      <c r="D38" s="1">
-        <v>10</v>
-      </c>
-      <c r="E38" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="1">
-        <v>2</v>
-      </c>
-      <c r="C39" s="1">
-        <v>8</v>
-      </c>
-      <c r="D39" s="1">
-        <v>10</v>
-      </c>
-      <c r="E39" s="1">
         <v>6</v>
       </c>
     </row>
